--- a/dataset_sesiones.xlsx
+++ b/dataset_sesiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1002"/>
+  <dimension ref="A1:I1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39514,6 +39514,45 @@
         <v>6</v>
       </c>
     </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2020-12-22</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Rio de la Plata</t>
+        </is>
+      </c>
+      <c r="C1003" t="n">
+        <v>120</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>21</v>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H1003" t="n">
+        <v>700</v>
+      </c>
+      <c r="I1003" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dataset_sesiones.xlsx
+++ b/dataset_sesiones.xlsx
@@ -39478,7 +39478,7 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>2018-03-20</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
@@ -39487,14 +39487,14 @@
         </is>
       </c>
       <c r="C1002" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="D1002" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
@@ -39511,7 +39511,7 @@
         <v>700</v>
       </c>
       <c r="I1002" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
